--- a/output/stock_quant_scores/BABA_info.xlsx
+++ b/output/stock_quant_scores/BABA_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FM2"/>
+  <dimension ref="A1:FQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,235 +1036,255 @@
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1367,34 +1387,34 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>163.08</v>
+        <v>175.47</v>
       </c>
       <c r="W2" t="n">
-        <v>175.98</v>
+        <v>172.17</v>
       </c>
       <c r="X2" t="n">
-        <v>175.04</v>
+        <v>169.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>180.16</v>
+        <v>172.76</v>
       </c>
       <c r="Z2" t="n">
-        <v>163.08</v>
+        <v>175.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>175.98</v>
+        <v>172.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>175.04</v>
+        <v>169.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>180.16</v>
+        <v>172.76</v>
       </c>
       <c r="AD2" t="n">
         <v>1.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="AF2" t="n">
         <v>1749686400</v>
@@ -1406,31 +1426,31 @@
         <v>0.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>20.31106</v>
+        <v>19.87399</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.86221</v>
+        <v>17.417427</v>
       </c>
       <c r="AK2" t="n">
-        <v>45524648</v>
+        <v>15889047</v>
       </c>
       <c r="AL2" t="n">
-        <v>45524648</v>
+        <v>15889047</v>
       </c>
       <c r="AM2" t="n">
-        <v>17102680</v>
+        <v>17987785</v>
       </c>
       <c r="AN2" t="n">
-        <v>24560600</v>
+        <v>24287420</v>
       </c>
       <c r="AO2" t="n">
-        <v>24560600</v>
+        <v>24287420</v>
       </c>
       <c r="AP2" t="n">
-        <v>176.41</v>
+        <v>172.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>176.49</v>
+        <v>172</v>
       </c>
       <c r="AR2" t="n">
         <v>3</v>
@@ -1439,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>425903357952</v>
+        <v>409919062016</v>
       </c>
       <c r="AU2" t="n">
         <v>80.06</v>
@@ -1454,19 +1474,19 @@
         <v>57.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.42557862</v>
+        <v>0.40960652</v>
       </c>
       <c r="AZ2" t="n">
-        <v>130.6052</v>
+        <v>134.0816</v>
       </c>
       <c r="BA2" t="n">
-        <v>117.00445</v>
+        <v>118.3485</v>
       </c>
       <c r="BB2" t="n">
         <v>7.619</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.046719402</v>
+        <v>0.043420527</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1477,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>2944893714432</v>
+        <v>3108866621440</v>
       </c>
       <c r="BG2" t="n">
         <v>0.14626001</v>
@@ -1486,34 +1506,34 @@
         <v>17611788000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2400409722</v>
+        <v>2384498036</v>
       </c>
       <c r="BJ2" t="n">
-        <v>35564358</v>
+        <v>43975803</v>
       </c>
       <c r="BK2" t="n">
-        <v>34195093</v>
+        <v>35532690</v>
       </c>
       <c r="BL2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0149</v>
+        <v>0.0184</v>
       </c>
       <c r="BO2" t="n">
         <v>0.00013</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.123009995</v>
+        <v>0.123059995</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0178</v>
+        <v>0.022</v>
       </c>
       <c r="BS2" t="n">
         <v>2575630080</v>
@@ -1522,7 +1542,7 @@
         <v>436.692</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.40371707</v>
+        <v>0.3936642</v>
       </c>
       <c r="BV2" t="n">
         <v>1743379200</v>
@@ -1540,22 +1560,22 @@
         <v>148316995584</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="CB2" t="n">
         <v>9.869999999999999</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.943</v>
+        <v>3.106</v>
       </c>
       <c r="CD2" t="n">
-        <v>15.904</v>
+        <v>16.381</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.7083595</v>
+        <v>0.6199585</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CG2" t="n">
         <v>2</v>
@@ -1569,22 +1589,22 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>176.3</v>
+        <v>171.91</v>
       </c>
       <c r="CK2" t="n">
-        <v>195.1668</v>
+        <v>267.07486</v>
       </c>
       <c r="CL2" t="n">
-        <v>131.22864</v>
+        <v>120.03366</v>
       </c>
       <c r="CM2" t="n">
-        <v>167.2378</v>
+        <v>179.84631</v>
       </c>
       <c r="CN2" t="n">
-        <v>166.70027</v>
+        <v>176.65543</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.30952</v>
+        <v>1.39535</v>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
@@ -1592,7 +1612,7 @@
         </is>
       </c>
       <c r="CQ2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CR2" t="n">
         <v>416414990336</v>
@@ -1601,7 +1621,7 @@
         <v>22.424</v>
       </c>
       <c r="CT2" t="n">
-        <v>185169002496</v>
+        <v>189780000768</v>
       </c>
       <c r="CU2" t="n">
         <v>253266001920</v>
@@ -1622,7 +1642,7 @@
         <v>430.407</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.04919</v>
+        <v>0.050780002</v>
       </c>
       <c r="DB2" t="n">
         <v>0.13447</v>
@@ -1631,7 +1651,7 @@
         <v>412154986496</v>
       </c>
       <c r="DD2" t="n">
-        <v>-33092499456</v>
+        <v>-30210625536</v>
       </c>
       <c r="DE2" t="n">
         <v>150545006592</v>
@@ -1646,7 +1666,7 @@
         <v>0.41184</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.18503</v>
+        <v>0.18964</v>
       </c>
       <c r="DJ2" t="n">
         <v>0.14128</v>
@@ -1691,172 +1711,184 @@
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>NYQ</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
+          <t>finmb_42083601</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-2.02884</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>171.91</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1758931189</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>17987785</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>91.85000599999999</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1.1472647</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>80.06 - 180.16</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.045792628</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>61.995853</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1752105600</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1755144000</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1763123400</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1763123400</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1756467000</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1756467000</v>
+      </c>
+      <c r="ES2" t="b">
+        <v>1</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>55.82565</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>3.079409</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>37.8284</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0.28212968</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>53.5615</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>0.45257437</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>1.4 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="FE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>1411133400000</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>0.27229008</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>172.3781</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>0.46809387</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
+          <t>169.7 - 172.76</t>
+        </is>
+      </c>
+      <c r="FM2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
           <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="FO2" t="inlineStr">
         <is>
           <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
-      <c r="DV2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1411133400000</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>13.220001</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>175.04 - 180.16</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>17102680</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>NYQ</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_42083601</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1758740035</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>8.106451</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>96.240005</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1.2020985</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>80.06 - 180.16</t>
-        </is>
-      </c>
-      <c r="EP2" t="n">
-        <v>-3.8600006</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.021425402</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>70.835945</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>1752105600</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1755144000</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>1763123400</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1763123400</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1756467000</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1756467000</v>
-      </c>
-      <c r="EY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>55.90681</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>3.153462</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>45.69481</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>0.34986976</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>59.295555</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>0.5067803</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>1.3 - Strong Buy</t>
-        </is>
-      </c>
-      <c r="FK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FL2" t="inlineStr">
+      <c r="FP2" t="inlineStr">
         <is>
           <t>Alibaba Group Holding</t>
         </is>
       </c>
-      <c r="FM2" t="n">
-        <v>1.8377</v>
+      <c r="FQ2" t="n">
+        <v>1.9366</v>
       </c>
     </row>
   </sheetData>
